--- a/reports/集团总公司_现金流量表_2026-04.xlsx
+++ b/reports/集团总公司_现金流量表_2026-04.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>200850000</v>
+        <v>196372418</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>755196000</v>
+        <v>741308049</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4026577</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>15098810</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1997960</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>7521355</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1004248</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>3777700</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>801542</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>3007568</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>600635</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2266207</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>402010</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1504793</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>299512</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1131876</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>201403</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>753445</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>498644</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1883542</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>253062</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>948098</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>158695</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>598042</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>545900</v>
+        <v>537552</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>2052584</v>
+        <v>2019865</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3708000</v>
+        <v>3639734</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>13942080</v>
+        <v>13671730</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>205103900</v>
+        <v>210793992</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>123600000</v>
+        <v>120909914</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>464736000</v>
+        <v>456894324</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1343058</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>5028228</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>997702</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3763415</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>670680</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2517361</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>499924</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1879936</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>334411</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1259301</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>252033</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>944793</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>24926000</v>
+        <v>24400428</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>93721760</v>
+        <v>92129922</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>11536000</v>
+        <v>11366125</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>43375360</v>
+        <v>42527439</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5253000</v>
+        <v>5130893</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>19751280</v>
+        <v>19391593</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>165315000</v>
+        <v>165905168</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>39788900</v>
+        <v>44888824</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>247200</v>
+        <v>242707</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>988800</v>
+        <v>974240</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2163000</v>
+        <v>2115723</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>8652000</v>
+        <v>8507399</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1318400</v>
+        <v>1301077</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>5273600</v>
+        <v>5176790</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2410200</v>
+        <v>2358430</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20600000</v>
+        <v>20276478</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>82400000</v>
+        <v>80795567</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2987000</v>
+        <v>2912117</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>11948000</v>
+        <v>11677198</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14626000</v>
+        <v>14376885</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>58504000</v>
+        <v>57461030</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>535600</v>
+        <v>524357</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>2142400</v>
+        <v>2107687</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>21135600</v>
+        <v>20800835</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18725400</v>
+        <v>-18442405</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4841000</v>
+        <v>4738109</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>19364000</v>
+        <v>19017721</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7725000</v>
+        <v>7571212</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>30900000</v>
+        <v>30292316</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7725000</v>
+        <v>7597283</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>30900000</v>
+        <v>30433838</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>247200</v>
+        <v>243160</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>988800</v>
+        <v>969687</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12813200</v>
+        <v>12552481</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6283000</v>
+        <v>6196740</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>25132000</v>
+        <v>24661412</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6283000</v>
+        <v>6147401</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>25132000</v>
+        <v>24721759</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1030000</v>
+        <v>1017010</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>4120000</v>
+        <v>4047564</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>896100</v>
+        <v>884344</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>3584400</v>
+        <v>3526899</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>128750</v>
+        <v>126075</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>515000</v>
+        <v>505009</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7441750</v>
+        <v>7339825</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5371450</v>
+        <v>5212656</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>26434950</v>
+        <v>31659075</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>26434950</v>
+        <v>31659075</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
